--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-practitioner-role.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-practitioner-role.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T06:36:19+00:00</t>
+    <t>2026-08-28T11:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3520,7 +3520,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>180</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>205</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>213</v>
       </c>
@@ -4438,7 +4438,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>229</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>242</v>
       </c>
@@ -5558,7 +5558,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>247</v>
       </c>
@@ -5660,7 +5660,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>249</v>
       </c>
@@ -5964,7 +5964,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>252</v>
       </c>
@@ -10650,12 +10650,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AJ88">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-practitioner-role.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-practitioner-role.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:20:46+00:00</t>
+    <t>2026-08-28T12:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-practitioner-role.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-practitioner-role.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:05:03+00:00</t>
+    <t>2026-08-28T12:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-practitioner-role.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-practitioner-role.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:17:39+00:00</t>
+    <t>2026-08-31T14:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
